--- a/output/pdf_financials_xlsx/ATI.H.xlsx
+++ b/output/pdf_financials_xlsx/ATI.H.xlsx
@@ -976,10 +976,10 @@
         <v>0.331728</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.413216</v>
+        <v>0.279508</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0</v>
+        <v>1.142027</v>
       </c>
     </row>
     <row r="11">
@@ -1038,10 +1038,10 @@
         <v>-0.14581</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.220631</v>
+        <v>-0.086923</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.108255</v>
+        <v>-1.033772</v>
       </c>
     </row>
     <row r="12">
@@ -38432,7 +38432,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -38511,10 +38511,10 @@
         </is>
       </c>
       <c r="T305" s="5" t="n">
-        <v>-0.279508</v>
+        <v>0.279508</v>
       </c>
       <c r="U305" s="5" t="n">
-        <v>-1.142027</v>
+        <v>1.142027</v>
       </c>
     </row>
     <row r="306">

--- a/output/pdf_financials_xlsx/ATI.H.xlsx
+++ b/output/pdf_financials_xlsx/ATI.H.xlsx
@@ -570,10 +570,8 @@
       <c r="C4" s="3" t="n">
         <v>0.057455</v>
       </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0.147286</v>
@@ -692,10 +690,8 @@
       <c r="C6" s="3" t="n">
         <v>0.057455</v>
       </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0.147286</v>
@@ -994,10 +990,8 @@
       <c r="C11" s="3" t="n">
         <v>-0.041156</v>
       </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D11" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>-10.074159</v>
@@ -1642,10 +1636,10 @@
         <v>0.039384</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>-0.023141</v>
+        <v>-0.086923</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>-1.009977</v>
+        <v>-1.015483</v>
       </c>
     </row>
     <row r="21">
@@ -1702,10 +1696,10 @@
         <v>0</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>0</v>
+        <v>0.06378200000000001</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>0</v>
+        <v>0.005506</v>
       </c>
     </row>
     <row r="22">
@@ -6912,16 +6906,16 @@
         <v>0</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.013971</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.010789</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.007713</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>0.005271</v>
       </c>
     </row>
     <row r="111">
@@ -6934,10 +6928,10 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000216</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.006335</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>-0.017436</v>
@@ -6970,10 +6964,10 @@
         <v>0</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00237</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00023</v>
       </c>
       <c r="Q111" s="3" t="n">
         <v>0</v>
@@ -7108,7 +7102,7 @@
         <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>-1.164338</v>
       </c>
       <c r="D114" s="3" t="n">
         <v>0</v>
@@ -7123,7 +7117,7 @@
         <v>0</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0</v>
+        <v>-0.273888</v>
       </c>
       <c r="I114" s="3" t="n">
         <v>0</v>
@@ -7169,37 +7163,37 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.105998</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.028825</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.034472</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.02325</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.03878</v>
       </c>
       <c r="J115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.030596</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.006125</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.000742</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="O115" s="3" t="n">
         <v>0</v>
@@ -8302,10 +8296,10 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000216</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.006335</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>-0.017436</v>
@@ -8338,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00237</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00023</v>
       </c>
       <c r="Q134" s="3" t="n">
         <v>0</v>
@@ -8360,10 +8354,10 @@
         <v>0.031086</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.143333</v>
+        <v>-0.143549</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>0.704713</v>
+        <v>0.6983780000000001</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-0.267486</v>
@@ -8396,10 +8390,10 @@
         <v>-0.010012</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>0.038157</v>
+        <v>0.035787</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>0.023455</v>
+        <v>0.023225</v>
       </c>
       <c r="Q135" s="3" t="n">
         <v>0.126621</v>
@@ -25431,7 +25425,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -28369,7 +28367,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -29521,7 +29523,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -32562,7 +32568,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -34663,7 +34673,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -34764,7 +34778,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -34865,7 +34883,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -36091,7 +36113,11 @@
           <t>Future income tax recoverable</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E282" s="5" t="n">
         <v>-0.054873</v>
       </c>
@@ -36594,7 +36620,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr">
         <is>
           <t>-</t>
@@ -38634,7 +38664,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -38733,7 +38767,11 @@
           <t>Net income from discontinued operations (Note 9)</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
@@ -48264,7 +48302,11 @@
           <t>NET EARNINGS (LOSS)</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr"/>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E405" t="inlineStr">
         <is>
           <t>-</t>
@@ -48866,7 +48908,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
           <t>-</t>
